--- a/erp-server/erp-server-scm/src/main/resources/excel/srmPurchaseOrder.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/srmPurchaseOrder.xlsx
@@ -61,7 +61,7 @@
     <t>价税合计</t>
   </si>
   <si>
-    <t>待收货入库量</t>
+    <t>剩余送货量</t>
   </si>
   <si>
     <t>已送货数量</t>

--- a/erp-server/erp-server-scm/src/main/resources/excel/srmPurchaseOrder.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/srmPurchaseOrder.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>下单时间</t>
   </si>
@@ -37,6 +37,9 @@
     <t>订单单号</t>
   </si>
   <si>
+    <t>单据类型</t>
+  </si>
+  <si>
     <t>执行状态</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
   </si>
   <si>
     <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.typeName}</t>
   </si>
   <si>
     <t>{.executionStatusName}</t>
@@ -1122,26 +1128,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
     <col min="2" max="2" width="27.375" customWidth="1"/>
-    <col min="3" max="3" width="19.375" customWidth="1"/>
-    <col min="4" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="22.875" customWidth="1"/>
-    <col min="7" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="19.5" customWidth="1"/>
-    <col min="12" max="12" width="21.75" customWidth="1"/>
-    <col min="13" max="14" width="20.25" customWidth="1"/>
-    <col min="15" max="15" width="24.375" customWidth="1"/>
-    <col min="16" max="16" width="29.5" customWidth="1"/>
-    <col min="17" max="17" width="16.75" customWidth="1"/>
+    <col min="3" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="22.875" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="22.875" customWidth="1"/>
+    <col min="8" max="9" width="17.625" customWidth="1"/>
+    <col min="10" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="19.5" customWidth="1"/>
+    <col min="13" max="13" width="21.75" customWidth="1"/>
+    <col min="14" max="15" width="20.25" customWidth="1"/>
+    <col min="16" max="16" width="24.375" customWidth="1"/>
+    <col min="17" max="17" width="29.5" customWidth="1"/>
+    <col min="18" max="18" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1160,22 +1166,22 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
@@ -1190,65 +1196,71 @@
       <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:17">
+    <row r="2" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="7" spans="16:16">
-      <c r="P7" s="5"/>
+    <row r="7" spans="1:18">
+      <c r="Q7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
